--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-observation-sur-echelle-douleur.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-observation-sur-echelle-douleur.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3545" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3545" uniqueCount="354">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -830,6 +830,10 @@
   </si>
   <si>
     <t>ED.thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
   </si>
   <si>
     <t>Observation.statusCode</t>
@@ -7386,7 +7390,7 @@
         <v>74</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>74</v>
+        <v>266</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>74</v>
@@ -7394,10 +7398,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7423,10 +7427,10 @@
         <v>91</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7457,7 +7461,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>74</v>
@@ -7475,7 +7479,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7495,10 +7499,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7596,10 +7600,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7640,7 +7644,7 @@
         <v>74</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>74</v>
@@ -7699,10 +7703,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7802,10 +7806,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7905,10 +7909,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8008,10 +8012,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8111,10 +8115,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8212,10 +8216,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8313,10 +8317,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8416,10 +8420,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8519,10 +8523,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8622,10 +8626,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8648,13 +8652,13 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -8705,7 +8709,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8725,10 +8729,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8751,7 +8755,7 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -8784,7 +8788,7 @@
       </c>
       <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>74</v>
@@ -8802,7 +8806,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8822,10 +8826,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8848,7 +8852,7 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -8901,7 +8905,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8921,10 +8925,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8980,25 +8984,25 @@
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF74" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -9018,10 +9022,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9044,13 +9048,13 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -9101,7 +9105,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9121,10 +9125,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9147,13 +9151,13 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -9184,7 +9188,7 @@
       </c>
       <c r="Y76" s="2"/>
       <c r="Z76" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>74</v>
@@ -9202,7 +9206,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9222,10 +9226,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9248,7 +9252,7 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
@@ -9281,25 +9285,25 @@
       </c>
       <c r="Y77" s="2"/>
       <c r="Z77" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF77" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9319,10 +9323,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9348,10 +9352,10 @@
         <v>170</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -9402,7 +9406,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -9422,10 +9426,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9523,10 +9527,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9626,10 +9630,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9729,10 +9733,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9832,10 +9836,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9935,10 +9939,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10038,10 +10042,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10139,10 +10143,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10240,10 +10244,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10343,10 +10347,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10446,10 +10450,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10549,10 +10553,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10575,7 +10579,7 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
@@ -10628,7 +10632,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -10648,10 +10652,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10674,7 +10678,7 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
@@ -10727,7 +10731,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -10747,10 +10751,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10773,7 +10777,7 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
@@ -10826,7 +10830,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -10846,10 +10850,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10872,7 +10876,7 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
@@ -10925,7 +10929,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -10945,10 +10949,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -10971,7 +10975,7 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
@@ -11024,7 +11028,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -11044,10 +11048,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11070,7 +11074,7 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L95" s="2"/>
       <c r="M95" s="2"/>
@@ -11123,7 +11127,7 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -11143,10 +11147,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11169,7 +11173,7 @@
         <v>74</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
@@ -11222,7 +11226,7 @@
         <v>74</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -11242,10 +11246,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11268,7 +11272,7 @@
         <v>74</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L97" s="2"/>
       <c r="M97" s="2"/>
@@ -11321,7 +11325,7 @@
         <v>74</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -11341,10 +11345,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11367,7 +11371,7 @@
         <v>74</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L98" s="2"/>
       <c r="M98" s="2"/>
@@ -11420,7 +11424,7 @@
         <v>74</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -11440,10 +11444,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11466,7 +11470,7 @@
         <v>74</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L99" s="2"/>
       <c r="M99" s="2"/>
@@ -11519,7 +11523,7 @@
         <v>74</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -11539,10 +11543,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11565,11 +11569,11 @@
         <v>74</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L100" s="2"/>
       <c r="M100" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -11620,7 +11624,7 @@
         <v>74</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -11640,10 +11644,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11741,10 +11745,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11842,10 +11846,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -11943,10 +11947,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12044,10 +12048,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12147,10 +12151,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12250,10 +12254,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12353,10 +12357,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12456,10 +12460,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12557,10 +12561,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12594,7 +12598,7 @@
       </c>
       <c r="Q110" s="2"/>
       <c r="R110" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="S110" t="s" s="2">
         <v>74</v>
@@ -12616,7 +12620,7 @@
       </c>
       <c r="Y110" s="2"/>
       <c r="Z110" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>74</v>
@@ -12634,7 +12638,7 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -12654,10 +12658,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -12680,7 +12684,7 @@
         <v>74</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
@@ -12733,7 +12737,7 @@
         <v>74</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>75</v>
@@ -12753,10 +12757,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -12779,7 +12783,7 @@
         <v>74</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
@@ -12832,7 +12836,7 @@
         <v>74</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
